--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619AADF0-2A99-4564-8CAD-A5234C1EF6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9091E5-BC28-4700-A38D-D6E3B9E8A4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Worked on C++ practice and completed college assignments</t>
+  </si>
+  <si>
+    <t>Attended classes and spent some time on fitness and study</t>
   </si>
 </sst>
 </file>
@@ -1079,27 +1082,51 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60</v>
+      </c>
+      <c r="D8" s="14">
+        <v>220</v>
+      </c>
+      <c r="E8" s="14">
+        <v>65</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>90</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1215</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>225</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9091E5-BC28-4700-A38D-D6E3B9E8A4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B78725-F901-4947-BAE8-DCC72B64C2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>Attended classes and spent some time on fitness and study</t>
+  </si>
+  <si>
+    <t>Focused on studying and completed my daily targets.</t>
   </si>
 </sst>
 </file>
@@ -1128,27 +1131,51 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>50</v>
+      </c>
+      <c r="D9" s="14">
+        <v>300</v>
+      </c>
+      <c r="E9" s="14">
+        <v>75</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B78725-F901-4947-BAE8-DCC72B64C2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9663021C-7E2F-4FB5-81BC-4AD7EE7D773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t>Focused on studying and completed my daily targets.</t>
+  </si>
+  <si>
+    <t>Weekend project work and self-study.</t>
+  </si>
+  <si>
+    <t>Regular college day with study and coding practice.</t>
   </si>
 </sst>
 </file>
@@ -1177,49 +1183,97 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>300</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>150</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>50</v>
+      </c>
+      <c r="D11" s="14">
+        <v>250</v>
+      </c>
+      <c r="E11" s="14">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14">
+        <v>150</v>
+      </c>
+      <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>150</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9663021C-7E2F-4FB5-81BC-4AD7EE7D773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789A7CE-AB53-432E-9817-2C9FB209BEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>Regular college day with study and coding practice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complete day to day work </t>
   </si>
 </sst>
 </file>
@@ -1276,26 +1279,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>40</v>
+      </c>
+      <c r="D12" s="14">
+        <v>180</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>180</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4789A7CE-AB53-432E-9817-2C9FB209BEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB05710-CA95-482A-B721-8CBCCFD7DFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t xml:space="preserve">complete day to day work </t>
+  </si>
+  <si>
+    <t>Worked on project development and coding</t>
   </si>
 </sst>
 </file>
@@ -1324,27 +1327,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>240</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB05710-CA95-482A-B721-8CBCCFD7DFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA49A99-A88F-4481-85DD-103DD67EB906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1373,27 +1373,51 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="14">
+        <v>200</v>
+      </c>
+      <c r="E14" s="14">
+        <v>50</v>
+      </c>
+      <c r="F14" s="14">
+        <v>6</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>150</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>876</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>564</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA49A99-A88F-4481-85DD-103DD67EB906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F44074-6D86-457C-984E-9B9D219DBDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Worked on project development and coding</t>
+  </si>
+  <si>
+    <t>Revision, coding practice and some rest.</t>
   </si>
 </sst>
 </file>
@@ -1419,27 +1422,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>108</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>180</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>884</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>556</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F44074-6D86-457C-984E-9B9D219DBDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915F624-6B3B-4DC1-A41C-329613FEEB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>Revision, coding practice and some rest.</t>
+  </si>
+  <si>
+    <t>Revised networking and cybersecurity concepts.</t>
   </si>
 </sst>
 </file>
@@ -1468,27 +1471,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>50</v>
+      </c>
+      <c r="D16" s="14">
+        <v>150</v>
+      </c>
+      <c r="E16" s="14">
+        <v>50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>220</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915F624-6B3B-4DC1-A41C-329613FEEB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25BFBD8-180E-4B0D-B041-2C975E7E1CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Revised networking and cybersecurity concepts.</t>
+  </si>
+  <si>
+    <t>Revision, coding practice and some rest</t>
+  </si>
+  <si>
+    <t>Worked on project development and coding.</t>
   </si>
 </sst>
 </file>
@@ -1517,49 +1523,97 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>180</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>40</v>
+      </c>
+      <c r="D18" s="14">
+        <v>150</v>
+      </c>
+      <c r="E18" s="14">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>3</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>150</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>813</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>627</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25BFBD8-180E-4B0D-B041-2C975E7E1CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37425191-671C-4EE1-B059-9B506EAC8E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Worked on project development and coding.</t>
+  </si>
+  <si>
+    <t>Attended college and practiced C++</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1405,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="14">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
@@ -1412,11 +1415,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>876</v>
+        <v>1170</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>564</v>
+        <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>55</v>
@@ -1448,7 +1451,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
@@ -1458,11 +1461,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>884</v>
+        <v>1178</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>556</v>
+        <v>262</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1586,7 +1589,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
@@ -1596,11 +1599,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>813</v>
+        <v>960</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>627</v>
+        <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
@@ -1615,27 +1618,51 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>180</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37425191-671C-4EE1-B059-9B506EAC8E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF9B245-A852-46CA-8E55-2130B56C691B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Attended college and practiced C++</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solving codeing problem and perpare for ca  </t>
   </si>
 </sst>
 </file>
@@ -1664,27 +1670,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46236</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>180</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF9B245-A852-46CA-8E55-2130B56C691B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A18E66-6262-497A-B0E6-C45E60D333BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -249,7 +249,10 @@
     <t>High</t>
   </si>
   <si>
-    <t xml:space="preserve">solving codeing problem and perpare for ca  </t>
+    <t xml:space="preserve">solving codeing problem and prepare for ca  </t>
+  </si>
+  <si>
+    <t>Good balance between classes, study and coding. Felt productive.</t>
   </si>
 </sst>
 </file>
@@ -1716,27 +1719,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46237</v>
+      </c>
+      <c r="B21" s="14">
+        <v>400</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>240</v>
+      </c>
+      <c r="E21" s="14">
+        <v>50</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>180</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A18E66-6262-497A-B0E6-C45E60D333BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318B7A7C-A382-4624-9885-C82C5983AE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Good balance between classes, study and coding. Felt productive.</t>
+  </si>
+  <si>
+    <t>attending seminar  and kenw about college features</t>
   </si>
 </sst>
 </file>
@@ -1765,27 +1768,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46238</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>50</v>
+      </c>
+      <c r="D22" s="14">
+        <v>180</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>180</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12612391.xlsx
+++ b/12612391.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s4ty4m\Desktop\daily life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318B7A7C-A382-4624-9885-C82C5983AE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F04C38E-754C-4F2D-9D10-25AF72EB37F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>attending seminar  and kenw about college features</t>
+  </si>
+  <si>
+    <t>Weekend project work and self-study</t>
   </si>
 </sst>
 </file>
@@ -1814,27 +1817,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46239</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>250</v>
+      </c>
+      <c r="E23" s="14">
+        <v>50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
